--- a/策划/excel/14_ShopEvent.xlsx
+++ b/策划/excel/14_ShopEvent.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27765" windowHeight="9540"/>
+    <workbookView windowWidth="27315" windowHeight="10470"/>
   </bookViews>
   <sheets>
     <sheet name="14_ShopEvent" sheetId="1" r:id="rId1"/>
@@ -32,12 +32,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
   <si>
     <t>编号【KEY】</t>
   </si>
   <si>
-    <t>售卖各等级卡牌数量（等级由1-3）</t>
+    <t>售卖各等级卡牌数量：[1级数量,2级数量,3级数量]；展示按等级从低到高排序，不足数量时取该等级全部卡牌</t>
   </si>
   <si>
     <t>事件名称</t>
@@ -73,13 +73,67 @@
     <t>client</t>
   </si>
   <si>
-    <t>[1,1,1]</t>
-  </si>
-  <si>
-    <t>旅行的精灵商人</t>
-  </si>
-  <si>
-    <t>云游四方的精灵商人牵着负重的地龙停下脚步，鞍袋与木箱里装满了稀奇货物。他微笑着向你招手，似乎愿意做一笔公平的交易。</t>
+    <t>[2,2,2]</t>
+  </si>
+  <si>
+    <t>诸神遗物商人</t>
+  </si>
+  <si>
+    <t>阿斯加德的商人摆开藏品，邀你挑选下一场战斗需要的卡牌。</t>
+  </si>
+  <si>
+    <t>米德加德行商</t>
+  </si>
+  <si>
+    <t>旅商在路口停下，箱中备有适合继续冒险的卡牌。</t>
+  </si>
+  <si>
+    <t>丰饶林地商人</t>
+  </si>
+  <si>
+    <t>华纳海姆的商人将林地收集的卡牌摆在树荫下。</t>
+  </si>
+  <si>
+    <t>光林秘货商人</t>
+  </si>
+  <si>
+    <t>亚尔夫海姆的光林间，一位商人展示珍藏的卡牌。</t>
+  </si>
+  <si>
+    <t>荒原补给商人</t>
+  </si>
+  <si>
+    <t>约顿海姆的荒原上，商人提供下一段旅程所需的卡牌。</t>
+  </si>
+  <si>
+    <t>地下锻炉商人</t>
+  </si>
+  <si>
+    <t>尼达维勒的锻炉旁，商人整理着待售的卡牌。</t>
+  </si>
+  <si>
+    <t>寒雾旅店商人</t>
+  </si>
+  <si>
+    <t>尼福尔海姆的寒雾中，旅店商人向你展示卡牌。</t>
+  </si>
+  <si>
+    <t>熔火驿站商人</t>
+  </si>
+  <si>
+    <t>穆斯贝尔海姆的驿站里，商人摆出耐热的卡牌箱。</t>
+  </si>
+  <si>
+    <t>冥河渡口商人</t>
+  </si>
+  <si>
+    <t>赫尔海姆的渡口旁，商人安静地等待你挑选卡牌。</t>
+  </si>
+  <si>
+    <t>跨界流浪商人</t>
+  </si>
+  <si>
+    <t>一位往返各界的流浪商人打开背包，拿出可购买的卡牌。</t>
   </si>
 </sst>
 </file>
@@ -92,7 +146,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -548,154 +609,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1107,10 +1168,10 @@
         <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:4">
@@ -1121,10 +1182,10 @@
         <v>13</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:4">
@@ -1135,10 +1196,10 @@
         <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:4">
@@ -1149,10 +1210,10 @@
         <v>13</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:4">
@@ -1163,10 +1224,10 @@
         <v>13</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:4">
@@ -1177,10 +1238,10 @@
         <v>13</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:4">
@@ -1191,10 +1252,10 @@
         <v>13</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:4">
@@ -1205,10 +1266,10 @@
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:4">
@@ -1219,10 +1280,10 @@
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:4">

--- a/策划/excel/14_ShopEvent.xlsx
+++ b/策划/excel/14_ShopEvent.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27315" windowHeight="10470"/>
+    <workbookView windowWidth="25935" windowHeight="15735"/>
   </bookViews>
   <sheets>
     <sheet name="14_ShopEvent" sheetId="1" r:id="rId1"/>
@@ -146,14 +146,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -609,154 +602,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1072,8 +1065,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="25.375" customWidth="1"/>
-    <col min="2" max="2" width="42.25" customWidth="1"/>
-    <col min="3" max="3" width="49.75" customWidth="1"/>
+    <col min="2" max="2" width="92.875" customWidth="1"/>
+    <col min="3" max="3" width="21.5" customWidth="1"/>
+    <col min="4" max="4" width="57.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:4">
